--- a/labs/lab-07-build-the-finance-sharepoint-site-and-load-finance-data/northstar-sharepoint-build-starter.xlsx
+++ b/labs/lab-07-build-the-finance-sharepoint-site-and-load-finance-data/northstar-sharepoint-build-starter.xlsx
@@ -27,7 +27,7 @@
     <t>Course</t>
   </si>
   <si>
-    <t>Generative AI for Finance and Fintech (TGS-2026065050)</t>
+    <t>Microsoft Copilot for Finance (TGS-2026065050)</t>
   </si>
   <si>
     <t>TSC mapping</t>
